--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
+        <v>57309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57311</v>
+        <v>57393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57393</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100110</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Gråspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picus canus</t>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>57404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100110</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57404</v>
+        <v>57405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -806,11 +806,11 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57250</v>
+        <v>57436</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57436</v>
+        <v>57439</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57439</v>
+        <v>57445</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57445</v>
+        <v>57448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57448</v>
+        <v>57449</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,137 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125433877</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58152</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Orsil, Orsilängarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>617997</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6928735</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Wallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Wallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125433877</v>
       </c>
       <c r="B4" t="n">
-        <v>58152</v>
+        <v>58256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -932,12 +932,7 @@
         <v>125433877</v>
       </c>
       <c r="B4" t="n">
-        <v>58256</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>125433877</v>
       </c>
       <c r="B4" t="n">
-        <v>58275</v>
+        <v>58276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,200 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126554094</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57787</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>618080</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6928929</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126554093</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57787</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>618023</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928846</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57655</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57665</v>
+        <v>57676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>118004226</v>
       </c>
       <c r="B2" t="n">
-        <v>57676</v>
+        <v>57945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,16 +801,11 @@
         <v>118379244</v>
       </c>
       <c r="B3" t="n">
-        <v>57449</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -924,67 +919,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125433877</v>
+        <v>126554059</v>
       </c>
       <c r="B4" t="n">
-        <v>58276</v>
+        <v>57774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103051</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orsil, Orsilängarna, Mpd</t>
+          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617997</v>
+        <v>617928</v>
       </c>
       <c r="R4" t="n">
-        <v>6928735</v>
+        <v>6928733</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +984,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:21</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:21</t>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,60 +1009,74 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Wallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Wallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126554094</v>
+        <v>126703942</v>
       </c>
       <c r="B5" t="n">
-        <v>57787</v>
+        <v>58463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205976</v>
+        <v>102995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
+          <t>Orsil, Orsilängarna, vid vägen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618080</v>
+        <v>618061</v>
       </c>
       <c r="R5" t="n">
-        <v>6928929</v>
+        <v>6928871</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,12 +1100,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annika Wallin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annika Wallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126554093</v>
+        <v>125433877</v>
       </c>
       <c r="B6" t="n">
-        <v>57787</v>
+        <v>58586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,37 +1153,56 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205976</v>
+        <v>103051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
+          <t>Orsil, Orsilängarna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618023</v>
+        <v>617997</v>
       </c>
       <c r="R6" t="n">
-        <v>6928846</v>
+        <v>6928735</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1226,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,74 +1256,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annika Wallin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Annika Wallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126703942</v>
+        <v>126554093</v>
       </c>
       <c r="B7" t="n">
-        <v>58162</v>
+        <v>58085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>205976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orsil, Orsilängarna, vid vägen, Mpd</t>
+          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618061</v>
+        <v>618023</v>
       </c>
       <c r="R7" t="n">
-        <v>6928871</v>
+        <v>6928846</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,22 +1333,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1353,214 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Wallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Wallin</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126554094</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östra Laggarbergsvägen, Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618080</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>73275118</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder om Hamstavägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>618002</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-05-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-05-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Längs ett bäckflöde i biotopen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Muntlin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Muntlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19449-2024 artfynd.xlsx
+++ b/artfynd/A 19449-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118004226</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118379244</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126554059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126703942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125433877</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126554093</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126554094</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,8 +1601,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73275118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>